--- a/data/trans_orig/DC-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DC-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2007</t>
+          <t>Población con dolor crónico en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>49324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>41065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67820</t>
+          <t>67846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74562</t>
+          <t>74411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109193</t>
+          <t>107885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224556</t>
+          <t>223686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246783</t>
+          <t>246312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193018</t>
+          <t>192992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219134</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>424655</t>
+          <t>425963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>459286</t>
+          <t>459437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91593</t>
+          <t>91843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127787</t>
+          <t>128141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204504</t>
+          <t>204775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247688</t>
+          <t>248512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>307528</t>
+          <t>305420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>367236</t>
+          <t>364709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365288</t>
+          <t>364934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401482</t>
+          <t>401232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256261</t>
+          <t>255437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299445</t>
+          <t>299174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>629788</t>
+          <t>632315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689496</t>
+          <t>691604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44629</t>
+          <t>44043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58232</t>
+          <t>55885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86572</t>
+          <t>86347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85188</t>
+          <t>86693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125595</t>
+          <t>123364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274217</t>
+          <t>274803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295812</t>
+          <t>296634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248840</t>
+          <t>249065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277180</t>
+          <t>279527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528663</t>
+          <t>530894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>569070</t>
+          <t>567565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88209</t>
+          <t>88410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65313</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97798</t>
+          <t>96445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132732</t>
+          <t>130494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176215</t>
+          <t>176594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270462</t>
+          <t>270261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301113</t>
+          <t>299234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273658</t>
+          <t>275011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306143</t>
+          <t>306514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553912</t>
+          <t>553533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>597395</t>
+          <t>599633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>23910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51587</t>
+          <t>51546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69259</t>
+          <t>69296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180476</t>
+          <t>179398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194896</t>
+          <t>194540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156081</t>
+          <t>156122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178235</t>
+          <t>179468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341717</t>
+          <t>341680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370939</t>
+          <t>369849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56955</t>
+          <t>56949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60253</t>
+          <t>61940</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90623</t>
+          <t>90810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101565</t>
+          <t>101406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139191</t>
+          <t>138193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213856</t>
+          <t>213862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237733</t>
+          <t>237511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187521</t>
+          <t>187334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217891</t>
+          <t>216204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409764</t>
+          <t>410762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>447390</t>
+          <t>447549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85046</t>
+          <t>82877</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121223</t>
+          <t>118422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110684</t>
+          <t>110266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151538</t>
+          <t>149108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201285</t>
+          <t>202172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255093</t>
+          <t>257605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>493804</t>
+          <t>496605</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>529981</t>
+          <t>532150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>486681</t>
+          <t>489111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527535</t>
+          <t>527953</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>998153</t>
+          <t>995641</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1051961</t>
+          <t>1051074</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>143755</t>
+          <t>142166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189099</t>
+          <t>187783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238153</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>294446</t>
+          <t>292012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>399488</t>
+          <t>396001</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>467590</t>
+          <t>464780</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>554696</t>
+          <t>556012</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>600040</t>
+          <t>601629</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>489065</t>
+          <t>491499</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>545358</t>
+          <t>543126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1059716</t>
+          <t>1062526</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1127818</t>
+          <t>1131305</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>534641</t>
+          <t>532336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>619071</t>
+          <t>618642</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>893553</t>
+          <t>887963</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>999137</t>
+          <t>995197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1444561</t>
+          <t>1447744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1583231</t>
+          <t>1578929</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2657472</t>
+          <t>2657901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2741902</t>
+          <t>2744207</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2380060</t>
+          <t>2384000</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2485644</t>
+          <t>2491234</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5072510</t>
+          <t>5076812</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5211180</t>
+          <t>5207997</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2012</t>
+          <t>Población con dolor crónico en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58887</t>
+          <t>60234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91642</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81130</t>
+          <t>82112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119859</t>
+          <t>120539</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259937</t>
+          <t>260063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278505</t>
+          <t>279167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195603</t>
+          <t>194778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228358</t>
+          <t>227011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462124</t>
+          <t>461444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>500853</t>
+          <t>499871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50128</t>
+          <t>49076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>87664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124651</t>
+          <t>125587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>116635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163867</t>
+          <t>162914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455399</t>
+          <t>456451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481096</t>
+          <t>481413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399114</t>
+          <t>398178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436205</t>
+          <t>436101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>865425</t>
+          <t>866378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>911384</t>
+          <t>912657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40241</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82847</t>
+          <t>85943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77906</t>
+          <t>79093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114523</t>
+          <t>116138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283805</t>
+          <t>284849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305082</t>
+          <t>305754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258173</t>
+          <t>255077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288498</t>
+          <t>287488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>550543</t>
+          <t>548928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>587160</t>
+          <t>585973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58616</t>
+          <t>57136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89268</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124684</t>
+          <t>125479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127252</t>
+          <t>125243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172380</t>
+          <t>172230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315366</t>
+          <t>316846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341935</t>
+          <t>342729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264267</t>
+          <t>263472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299683</t>
+          <t>298928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>590553</t>
+          <t>590703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>635681</t>
+          <t>637690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47814</t>
+          <t>47924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73061</t>
+          <t>72072</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101691</t>
+          <t>100784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>103348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143047</t>
+          <t>140596</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164804</t>
+          <t>164694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187706</t>
+          <t>187367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117900</t>
+          <t>118807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146530</t>
+          <t>147519</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>289162</t>
+          <t>291613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328184</t>
+          <t>328861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>55038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>62069</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91703</t>
+          <t>92104</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99292</t>
+          <t>99055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138131</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219212</t>
+          <t>218943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243126</t>
+          <t>243324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188328</t>
+          <t>187927</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219080</t>
+          <t>217962</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>415881</t>
+          <t>416140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>454720</t>
+          <t>454957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64136</t>
+          <t>64673</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98015</t>
+          <t>99498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>161095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208619</t>
+          <t>209290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232655</t>
+          <t>234540</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294995</t>
+          <t>294045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>564773</t>
+          <t>563290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598652</t>
+          <t>598115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>485234</t>
+          <t>484563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>532873</t>
+          <t>532758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1061646</t>
+          <t>1062596</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1123986</t>
+          <t>1122101</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>52841</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84281</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125679</t>
+          <t>123152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>170533</t>
+          <t>168917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187139</t>
+          <t>186407</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243669</t>
+          <t>243264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694817</t>
+          <t>693992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727034</t>
+          <t>726257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>653320</t>
+          <t>654936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>698174</t>
+          <t>700701</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1359282</t>
+          <t>1359687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1415812</t>
+          <t>1416544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>322100</t>
+          <t>321648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>392294</t>
+          <t>393929</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>798128</t>
+          <t>795179</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>901736</t>
+          <t>899494</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1134634</t>
+          <t>1141083</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1266868</t>
+          <t>1274004</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3034485</t>
+          <t>3032850</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3104679</t>
+          <t>3105131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2656573</t>
+          <t>2658815</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2760181</t>
+          <t>2763130</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5718220</t>
+          <t>5711084</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5850454</t>
+          <t>5844005</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2016</t>
+          <t>Población con dolor crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>43566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>59678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90037</t>
+          <t>90447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88346</t>
+          <t>86825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125129</t>
+          <t>126071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250533</t>
+          <t>250195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273145</t>
+          <t>271764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198666</t>
+          <t>198256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229491</t>
+          <t>229025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>457335</t>
+          <t>456393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>494118</t>
+          <t>495639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>42246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73537</t>
+          <t>74935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71156</t>
+          <t>71396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110027</t>
+          <t>108293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>458870</t>
+          <t>460329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481714</t>
+          <t>481453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449547</t>
+          <t>448149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478757</t>
+          <t>478947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915632</t>
+          <t>917366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954503</t>
+          <t>954263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36137</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>49539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79303</t>
+          <t>81735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72414</t>
+          <t>71189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108742</t>
+          <t>106936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282428</t>
+          <t>282272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301492</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257006</t>
+          <t>254574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287184</t>
+          <t>286770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546132</t>
+          <t>547938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582460</t>
+          <t>583685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28697</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53951</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77652</t>
+          <t>75891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>113241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110642</t>
+          <t>112387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153503</t>
+          <t>155176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316013</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341267</t>
+          <t>340829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274290</t>
+          <t>274042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309631</t>
+          <t>311392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>603744</t>
+          <t>602071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>646605</t>
+          <t>644860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>33719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>56187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>81925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177039</t>
+          <t>177502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196517</t>
+          <t>196303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163235</t>
+          <t>162400</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185792</t>
+          <t>186198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347706</t>
+          <t>347883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376859</t>
+          <t>378312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55166</t>
+          <t>56044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53396</t>
+          <t>52418</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86439</t>
+          <t>84645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225531</t>
+          <t>225661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245837</t>
+          <t>244893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217949</t>
+          <t>217071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242729</t>
+          <t>243006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449799</t>
+          <t>451593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482842</t>
+          <t>483820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90820</t>
+          <t>89199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127605</t>
+          <t>128731</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173686</t>
+          <t>173717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196876</t>
+          <t>197013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252069</t>
+          <t>254986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565738</t>
+          <t>567359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600652</t>
+          <t>600138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517608</t>
+          <t>517577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>563689</t>
+          <t>562563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1095783</t>
+          <t>1092866</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1150976</t>
+          <t>1150839</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59322</t>
+          <t>58580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93108</t>
+          <t>90583</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106917</t>
+          <t>106722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149893</t>
+          <t>148529</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175669</t>
+          <t>175064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231665</t>
+          <t>226888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>685475</t>
+          <t>688000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>719261</t>
+          <t>720003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>676274</t>
+          <t>677638</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>719250</t>
+          <t>719445</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373085</t>
+          <t>1377862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1429081</t>
+          <t>1429686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>286053</t>
+          <t>287743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>360552</t>
+          <t>357414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>600473</t>
+          <t>606242</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>694991</t>
+          <t>705030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>911753</t>
+          <t>915013</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1030591</t>
+          <t>1032720</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3033798</t>
+          <t>3036936</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3108297</t>
+          <t>3106607</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2849551</t>
+          <t>2839512</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2944069</t>
+          <t>2938300</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5908301</t>
+          <t>5906172</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6027139</t>
+          <t>6023879</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2023</t>
+          <t>Población con dolor crónico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53205</t>
+          <t>53601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>53712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74458</t>
+          <t>76387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86207</t>
+          <t>86563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119614</t>
+          <t>118534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258238</t>
+          <t>257842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282643</t>
+          <t>282802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215177</t>
+          <t>213248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236540</t>
+          <t>235923</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>481463</t>
+          <t>482543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514870</t>
+          <t>514514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77677</t>
+          <t>77945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123201</t>
+          <t>119902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173668</t>
+          <t>173863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212404</t>
+          <t>211007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260606</t>
+          <t>260368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322548</t>
+          <t>322365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395189</t>
+          <t>398488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440713</t>
+          <t>440445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302565</t>
+          <t>303962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341301</t>
+          <t>341106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710811</t>
+          <t>710994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>772753</t>
+          <t>772991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>59695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87078</t>
+          <t>88427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113113</t>
+          <t>113934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142809</t>
+          <t>143724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180061</t>
+          <t>180531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219418</t>
+          <t>221853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228972</t>
+          <t>227623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257220</t>
+          <t>256355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206319</t>
+          <t>205404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236015</t>
+          <t>235194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445760</t>
+          <t>443325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>485117</t>
+          <t>484647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,86%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41499</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>70290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143969</t>
+          <t>146216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312301</t>
+          <t>307145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192657</t>
+          <t>197114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>409628</t>
+          <t>394728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>242267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271058</t>
+          <t>271253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163417</t>
+          <t>168573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331749</t>
+          <t>329502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378646</t>
+          <t>393546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>595617</t>
+          <t>591160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42091</t>
+          <t>42608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37830</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93917</t>
+          <t>93444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70181</t>
+          <t>73895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125245</t>
+          <t>125950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136651</t>
+          <t>136134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152620</t>
+          <t>152821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164862</t>
+          <t>165335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220949</t>
+          <t>221879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312276</t>
+          <t>311571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367340</t>
+          <t>363626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63999</t>
+          <t>64766</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89991</t>
+          <t>90370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100317</t>
+          <t>100086</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125695</t>
+          <t>125515</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170867</t>
+          <t>173069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206370</t>
+          <t>206823</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179645</t>
+          <t>179266</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205637</t>
+          <t>204870</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131361</t>
+          <t>131541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156739</t>
+          <t>156970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>320322</t>
+          <t>319869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>355825</t>
+          <t>353623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>168655</t>
+          <t>168011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222832</t>
+          <t>220219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>468917</t>
+          <t>465836</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698234</t>
+          <t>706131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>636130</t>
+          <t>634767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1041515</t>
+          <t>1017705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>401447</t>
+          <t>404060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>455624</t>
+          <t>456268</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>151031</t>
+          <t>143134</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>380348</t>
+          <t>383429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>432029</t>
+          <t>455839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>837414</t>
+          <t>838777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>59251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>186332</t>
+          <t>187364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214904</t>
+          <t>213723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>258074</t>
+          <t>254737</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>231666</t>
+          <t>221953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>440292</t>
+          <t>441777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742388</t>
+          <t>741356</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>871699</t>
+          <t>869469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>459657</t>
+          <t>462994</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>502827</t>
+          <t>504008</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1206160</t>
+          <t>1204675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1414786</t>
+          <t>1424499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>558646</t>
+          <t>541691</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>774040</t>
+          <t>774077</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1402061</t>
+          <t>1405779</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1966429</t>
+          <t>1954309</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2040610</t>
+          <t>2046408</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2786276</t>
+          <t>2721471</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2685777</t>
+          <t>2685740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2901171</t>
+          <t>2918126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1745851</t>
+          <t>1757971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2310219</t>
+          <t>2306501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4385821</t>
+          <t>4450626</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5131487</t>
+          <t>5125689</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DC-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>48266</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67846</t>
+          <t>68490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74411</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107885</t>
+          <t>109358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223686</t>
+          <t>224744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246312</t>
+          <t>246098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192992</t>
+          <t>192348</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219773</t>
+          <t>219363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425963</t>
+          <t>424490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>459437</t>
+          <t>460233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91843</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128141</t>
+          <t>128224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204775</t>
+          <t>203826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248512</t>
+          <t>249436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305420</t>
+          <t>304948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>364709</t>
+          <t>364641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364934</t>
+          <t>364851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401232</t>
+          <t>401458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>255437</t>
+          <t>254513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299174</t>
+          <t>300123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>632315</t>
+          <t>632383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691604</t>
+          <t>692076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44043</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55885</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86347</t>
+          <t>88058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86693</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>123477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274803</t>
+          <t>273086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296634</t>
+          <t>297141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249065</t>
+          <t>247354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279527</t>
+          <t>277758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530894</t>
+          <t>530781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>567565</t>
+          <t>569045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59437</t>
+          <t>57567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88410</t>
+          <t>88359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64942</t>
+          <t>66355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96445</t>
+          <t>95307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130494</t>
+          <t>130761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176594</t>
+          <t>174657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270261</t>
+          <t>270312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299234</t>
+          <t>301104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275011</t>
+          <t>276149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306514</t>
+          <t>305101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553533</t>
+          <t>555470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>599633</t>
+          <t>599366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>29954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51546</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69296</t>
+          <t>70287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179398</t>
+          <t>179733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194540</t>
+          <t>194581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156122</t>
+          <t>155265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179468</t>
+          <t>177714</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341680</t>
+          <t>340689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369849</t>
+          <t>369912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33300</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>57696</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61940</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90810</t>
+          <t>90478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101406</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>139379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213862</t>
+          <t>213115</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237511</t>
+          <t>237452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187334</t>
+          <t>187666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216204</t>
+          <t>218127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>410762</t>
+          <t>409576</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>447549</t>
+          <t>448039</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110266</t>
+          <t>108802</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149108</t>
+          <t>150201</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202172</t>
+          <t>203007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257605</t>
+          <t>261008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>496605</t>
+          <t>497585</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>532150</t>
+          <t>532371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>489111</t>
+          <t>488018</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527953</t>
+          <t>529417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>995641</t>
+          <t>992238</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1051074</t>
+          <t>1050239</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142166</t>
+          <t>144508</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>187783</t>
+          <t>190700</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240385</t>
+          <t>237198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292012</t>
+          <t>289551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>396001</t>
+          <t>390264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>464780</t>
+          <t>462003</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>556012</t>
+          <t>553095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>601629</t>
+          <t>599287</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>491499</t>
+          <t>493960</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>543126</t>
+          <t>546313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1062526</t>
+          <t>1065303</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1131305</t>
+          <t>1137042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>532336</t>
+          <t>533223</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>618642</t>
+          <t>622922</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>887963</t>
+          <t>892353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>995197</t>
+          <t>999527</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1447744</t>
+          <t>1439946</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1578929</t>
+          <t>1579800</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2657901</t>
+          <t>2653621</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2744207</t>
+          <t>2743320</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2384000</t>
+          <t>2379670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2491234</t>
+          <t>2486844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5076812</t>
+          <t>5075941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5207997</t>
+          <t>5215795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60234</t>
+          <t>59756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92467</t>
+          <t>92932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82112</t>
+          <t>79869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120539</t>
+          <t>118358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260063</t>
+          <t>261121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279167</t>
+          <t>279795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194778</t>
+          <t>194313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227011</t>
+          <t>227489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461444</t>
+          <t>463625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499871</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87664</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125587</t>
+          <t>123708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116635</t>
+          <t>118086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162914</t>
+          <t>163101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456451</t>
+          <t>457192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481413</t>
+          <t>481416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398178</t>
+          <t>400057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436101</t>
+          <t>437066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>866378</t>
+          <t>866191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>912657</t>
+          <t>911206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>53167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85943</t>
+          <t>83335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79093</t>
+          <t>78698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116138</t>
+          <t>115454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284849</t>
+          <t>284456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305754</t>
+          <t>305190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255077</t>
+          <t>257685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287488</t>
+          <t>287853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548928</t>
+          <t>549612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585973</t>
+          <t>586368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57136</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>89414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125479</t>
+          <t>124798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125243</t>
+          <t>127347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172230</t>
+          <t>172892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316846</t>
+          <t>317213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342729</t>
+          <t>342450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263472</t>
+          <t>264153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>298928</t>
+          <t>299537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>590703</t>
+          <t>590041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>637690</t>
+          <t>635586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47924</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72072</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100784</t>
+          <t>100296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103348</t>
+          <t>103258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140596</t>
+          <t>142205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164694</t>
+          <t>165099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187367</t>
+          <t>187573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118807</t>
+          <t>119295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147519</t>
+          <t>148518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291613</t>
+          <t>290004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328861</t>
+          <t>328951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>54516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62069</t>
+          <t>60092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92104</t>
+          <t>90290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99055</t>
+          <t>99035</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137872</t>
+          <t>136973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218943</t>
+          <t>219465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243324</t>
+          <t>244256</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187927</t>
+          <t>189741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217962</t>
+          <t>219939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>416140</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>454957</t>
+          <t>454977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>64226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99498</t>
+          <t>98459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161095</t>
+          <t>159488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209290</t>
+          <t>209062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>234540</t>
+          <t>232385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294045</t>
+          <t>294009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563290</t>
+          <t>564329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598115</t>
+          <t>598562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>484563</t>
+          <t>484791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>532758</t>
+          <t>534365</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1062596</t>
+          <t>1062632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1122101</t>
+          <t>1124256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52841</t>
+          <t>53236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85106</t>
+          <t>86862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>123152</t>
+          <t>126095</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168917</t>
+          <t>170143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186407</t>
+          <t>185803</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243264</t>
+          <t>242782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>693992</t>
+          <t>692236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726257</t>
+          <t>725862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>654936</t>
+          <t>653710</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>700701</t>
+          <t>697758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1359687</t>
+          <t>1360169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1416544</t>
+          <t>1417148</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>321648</t>
+          <t>315704</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>393929</t>
+          <t>391960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>795179</t>
+          <t>795910</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>899494</t>
+          <t>895993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1141083</t>
+          <t>1135931</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1274004</t>
+          <t>1268886</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3032850</t>
+          <t>3034819</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3105131</t>
+          <t>3111075</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2658815</t>
+          <t>2662316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2763130</t>
+          <t>2762399</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5711084</t>
+          <t>5716202</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5844005</t>
+          <t>5849157</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59678</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>90088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86825</t>
+          <t>87243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126071</t>
+          <t>124741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250195</t>
+          <t>250142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271764</t>
+          <t>272731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198256</t>
+          <t>198615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229025</t>
+          <t>228780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>456393</t>
+          <t>457723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>495639</t>
+          <t>495221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42246</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44137</t>
+          <t>44779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74935</t>
+          <t>74703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71396</t>
+          <t>72099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108293</t>
+          <t>106211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460329</t>
+          <t>459033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481453</t>
+          <t>480642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448149</t>
+          <t>448381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478947</t>
+          <t>478305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917366</t>
+          <t>919448</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954263</t>
+          <t>953560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36293</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>49518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81735</t>
+          <t>80598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71189</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106936</t>
+          <t>107910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282272</t>
+          <t>281765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300723</t>
+          <t>301466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254574</t>
+          <t>255711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286770</t>
+          <t>286791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547938</t>
+          <t>546964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>583685</t>
+          <t>582620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54905</t>
+          <t>53217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75891</t>
+          <t>75867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113241</t>
+          <t>111305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112387</t>
+          <t>112964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155176</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315059</t>
+          <t>316747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>340829</t>
+          <t>342107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274042</t>
+          <t>275978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>311392</t>
+          <t>311416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>602071</t>
+          <t>601985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>644860</t>
+          <t>644283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33719</t>
+          <t>32127</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>52137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81925</t>
+          <t>83250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177502</t>
+          <t>179094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196303</t>
+          <t>196202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162400</t>
+          <t>161801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186198</t>
+          <t>185219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347883</t>
+          <t>346558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378312</t>
+          <t>377671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>56231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84645</t>
+          <t>84867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225661</t>
+          <t>225545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244893</t>
+          <t>246142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217071</t>
+          <t>216884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243006</t>
+          <t>241674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>451593</t>
+          <t>451371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>483820</t>
+          <t>482677</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>56283</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89199</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128731</t>
+          <t>128988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173717</t>
+          <t>172259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>197013</t>
+          <t>194655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254986</t>
+          <t>248900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567359</t>
+          <t>566739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600138</t>
+          <t>600275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517577</t>
+          <t>519035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>562563</t>
+          <t>562306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1092866</t>
+          <t>1098952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1150839</t>
+          <t>1153197</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58580</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90583</t>
+          <t>91836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106722</t>
+          <t>104926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148529</t>
+          <t>147795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175064</t>
+          <t>174608</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226888</t>
+          <t>227254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>688000</t>
+          <t>686747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720003</t>
+          <t>719823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>677638</t>
+          <t>678372</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>719445</t>
+          <t>721241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1377862</t>
+          <t>1377496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1429686</t>
+          <t>1430142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>287743</t>
+          <t>289786</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>357414</t>
+          <t>359789</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>606242</t>
+          <t>604553</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>705030</t>
+          <t>701740</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>915013</t>
+          <t>920510</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1032720</t>
+          <t>1034593</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3036936</t>
+          <t>3034561</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3106607</t>
+          <t>3104564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2839512</t>
+          <t>2842802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2938300</t>
+          <t>2939989</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5906172</t>
+          <t>5904299</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6023879</t>
+          <t>6018382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>40364</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>53273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63754</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53712</t>
+          <t>58822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76387</t>
+          <t>81647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>102377</t>
+          <t>109536</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>94676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118534</t>
+          <t>127405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>272819</t>
+          <t>278481</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257842</t>
+          <t>265572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282802</t>
+          <t>288682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>225881</t>
+          <t>246889</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213248</t>
+          <t>234414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235923</t>
+          <t>257239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>498700</t>
+          <t>525370</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482543</t>
+          <t>507501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514514</t>
+          <t>540230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>98130</t>
+          <t>101952</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77945</t>
+          <t>82475</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119902</t>
+          <t>125685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>191775</t>
+          <t>201154</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173863</t>
+          <t>181468</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>211007</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>289905</t>
+          <t>303105</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260368</t>
+          <t>271250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322365</t>
+          <t>332071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420260</t>
+          <t>428695</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398488</t>
+          <t>404962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440445</t>
+          <t>448172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>323194</t>
+          <t>345340</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303962</t>
+          <t>324798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341106</t>
+          <t>365026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>743454</t>
+          <t>774036</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710994</t>
+          <t>745070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>772991</t>
+          <t>805891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71830</t>
+          <t>72070</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59695</t>
+          <t>60311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88427</t>
+          <t>87644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>132586</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113934</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143724</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>199497</t>
+          <t>204657</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180531</t>
+          <t>184081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221853</t>
+          <t>224469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>244220</t>
+          <t>243923</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227623</t>
+          <t>228349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256355</t>
+          <t>255682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>221461</t>
+          <t>223795</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205404</t>
+          <t>208680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>237568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>465681</t>
+          <t>467718</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>443325</t>
+          <t>447906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>484647</t>
+          <t>488294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>58210</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70290</t>
+          <t>75703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202307</t>
+          <t>148137</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146216</t>
+          <t>131895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307145</t>
+          <t>167080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>257038</t>
+          <t>206347</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197114</t>
+          <t>181012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394728</t>
+          <t>229655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>257826</t>
+          <t>314935</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242267</t>
+          <t>297442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271253</t>
+          <t>329445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>273411</t>
+          <t>273824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168573</t>
+          <t>254881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329502</t>
+          <t>290066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>531236</t>
+          <t>588760</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393546</t>
+          <t>565452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>591160</t>
+          <t>614095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>29149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42608</t>
+          <t>47825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73005</t>
+          <t>77494</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>67535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93444</t>
+          <t>88086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>106367</t>
+          <t>114496</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73895</t>
+          <t>101418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125950</t>
+          <t>128752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>145381</t>
+          <t>168663</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>157840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152821</t>
+          <t>176516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>185774</t>
+          <t>151424</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165335</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>221879</t>
+          <t>161383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>331154</t>
+          <t>320086</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>311571</t>
+          <t>305830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363626</t>
+          <t>333164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77078</t>
+          <t>75694</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64766</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90370</t>
+          <t>86907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>114616</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100086</t>
+          <t>101810</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125515</t>
+          <t>127276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>189236</t>
+          <t>190309</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>173069</t>
+          <t>172562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206823</t>
+          <t>209165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>192558</t>
+          <t>195013</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179266</t>
+          <t>183800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204870</t>
+          <t>207167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>144898</t>
+          <t>149134</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131541</t>
+          <t>136474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156970</t>
+          <t>161940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>337456</t>
+          <t>344148</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319869</t>
+          <t>325292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353623</t>
+          <t>361895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>194307</t>
+          <t>224290</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>168011</t>
+          <t>195559</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220219</t>
+          <t>252309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>567108</t>
+          <t>439176</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>465836</t>
+          <t>413244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>706131</t>
+          <t>466159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>761415</t>
+          <t>663466</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>634767</t>
+          <t>621189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1017705</t>
+          <t>700146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>429972</t>
+          <t>495397</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>404060</t>
+          <t>467378</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>456268</t>
+          <t>524128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>282157</t>
+          <t>332881</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>143134</t>
+          <t>305898</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383429</t>
+          <t>358813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>712129</t>
+          <t>828278</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>455839</t>
+          <t>791598</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>838777</t>
+          <t>870555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>130630</t>
+          <t>147829</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>128911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>187364</t>
+          <t>170482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>234398</t>
+          <t>266531</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>213723</t>
+          <t>244578</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254737</t>
+          <t>291108</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>365028</t>
+          <t>414360</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>221953</t>
+          <t>382868</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>441777</t>
+          <t>444794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>798090</t>
+          <t>650243</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>741356</t>
+          <t>627590</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>869469</t>
+          <t>669161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>483333</t>
+          <t>564800</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>462994</t>
+          <t>540223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>504008</t>
+          <t>586753</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1281424</t>
+          <t>1215043</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1204675</t>
+          <t>1184609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1424499</t>
+          <t>1246535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>76,5%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>698690</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>541691</t>
+          <t>706662</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>774077</t>
+          <t>812902</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1572173</t>
+          <t>1448866</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1405779</t>
+          <t>1396088</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1954309</t>
+          <t>1501379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2270863</t>
+          <t>2206276</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2046408</t>
+          <t>2131668</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2721471</t>
+          <t>2284908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2761127</t>
+          <t>2775352</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2685740</t>
+          <t>2719860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2918126</t>
+          <t>2826100</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2140107</t>
+          <t>2288088</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1757971</t>
+          <t>2235575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2306501</t>
+          <t>2340866</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4901234</t>
+          <t>5063440</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4450626</t>
+          <t>4984808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5125689</t>
+          <t>5138048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
